--- a/input/16cut_non_AB.xlsx
+++ b/input/16cut_non_AB.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2704,10 +2704,10 @@
       <c r="D3" s="85" t="n">
         <v>1485</v>
       </c>
-      <c r="E3" s="303" t="n">
+      <c r="E3" s="310" t="n">
         <v>40</v>
       </c>
-      <c r="F3" s="303" t="n"/>
+      <c r="F3" s="310" t="n"/>
       <c r="G3" s="243">
         <f>E3-F3</f>
         <v/>
@@ -2717,7 +2717,7 @@
           <t>16cut/Jet Black AB/SS16/Non/002+</t>
         </is>
       </c>
-      <c r="I3" s="355" t="inlineStr">
+      <c r="I3" s="348" t="inlineStr">
         <is>
           <t>002+</t>
         </is>
@@ -2736,10 +2736,10 @@
       <c r="D4" s="86" t="n">
         <v>1972</v>
       </c>
-      <c r="E4" s="301" t="n">
+      <c r="E4" s="311" t="n">
         <v>49</v>
       </c>
-      <c r="F4" s="301" t="n"/>
+      <c r="F4" s="311" t="n"/>
       <c r="G4" s="245">
         <f>E4-F4</f>
         <v/>
@@ -2764,10 +2764,10 @@
       <c r="D5" s="87" t="n">
         <v>1485</v>
       </c>
-      <c r="E5" s="318" t="n">
+      <c r="E5" s="320" t="n">
         <v>39</v>
       </c>
-      <c r="F5" s="318" t="n"/>
+      <c r="F5" s="320" t="n"/>
       <c r="G5" s="247">
         <f>E5-F5</f>
         <v/>
@@ -2796,10 +2796,10 @@
       <c r="D6" s="85" t="n">
         <v>1647</v>
       </c>
-      <c r="E6" s="303" t="n">
+      <c r="E6" s="310" t="n">
         <v>50</v>
       </c>
-      <c r="F6" s="303">
+      <c r="F6" s="310">
         <f>1+1+2+1</f>
         <v/>
       </c>
@@ -2812,7 +2812,7 @@
           <t>16cut/Topaz AB/SS16/Non/008+</t>
         </is>
       </c>
-      <c r="I6" s="355" t="inlineStr">
+      <c r="I6" s="348" t="inlineStr">
         <is>
           <t>008+</t>
         </is>
@@ -2831,10 +2831,10 @@
       <c r="D7" s="87" t="n">
         <v>2133</v>
       </c>
-      <c r="E7" s="318" t="n">
+      <c r="E7" s="320" t="n">
         <v>80</v>
       </c>
-      <c r="F7" s="301">
+      <c r="F7" s="311">
         <f>6+2+2+3+2</f>
         <v/>
       </c>
@@ -2862,10 +2862,10 @@
       <c r="D8" s="88" t="n">
         <v>1647</v>
       </c>
-      <c r="E8" s="302" t="n">
+      <c r="E8" s="312" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="302">
+      <c r="F8" s="312">
         <f>1+1+2+1</f>
         <v/>
       </c>
@@ -2881,26 +2881,26 @@
       <c r="I8" s="429" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A9" s="303" t="inlineStr">
+      <c r="A9" s="310" t="inlineStr">
         <is>
           <t>Lt. Colorado Topaz AB</t>
         </is>
       </c>
-      <c r="B9" s="303" t="inlineStr">
+      <c r="B9" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C9" s="303" t="n">
+      <c r="C9" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D9" s="85" t="n">
         <v>1647</v>
       </c>
-      <c r="E9" s="338" t="n">
+      <c r="E9" s="329" t="n">
         <v>52</v>
       </c>
-      <c r="F9" s="303" t="n"/>
+      <c r="F9" s="310" t="n"/>
       <c r="G9" s="243">
         <f>E9-F9</f>
         <v/>
@@ -2910,7 +2910,7 @@
           <t>16cut/Lt.Colorado Topaz AB/SS16/Non/010+</t>
         </is>
       </c>
-      <c r="I9" s="355" t="inlineStr">
+      <c r="I9" s="348" t="inlineStr">
         <is>
           <t>010+</t>
         </is>
@@ -2918,21 +2918,21 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A10" s="427" t="n"/>
-      <c r="B10" s="301" t="inlineStr">
+      <c r="B10" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C10" s="301" t="n">
+      <c r="C10" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D10" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E10" s="336" t="n">
+      <c r="E10" s="330" t="n">
         <v>79</v>
       </c>
-      <c r="F10" s="301" t="n"/>
+      <c r="F10" s="311" t="n"/>
       <c r="G10" s="245">
         <f>E10-F10</f>
         <v/>
@@ -2946,21 +2946,21 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A11" s="431" t="n"/>
-      <c r="B11" s="302" t="inlineStr">
+      <c r="B11" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C11" s="302" t="n">
+      <c r="C11" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D11" s="88" t="n">
         <v>1647</v>
       </c>
-      <c r="E11" s="339" t="n">
+      <c r="E11" s="331" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="302" t="n"/>
+      <c r="F11" s="312" t="n"/>
       <c r="G11" s="246">
         <f>E11-F11</f>
         <v/>
@@ -2989,10 +2989,10 @@
       <c r="D12" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E12" s="317" t="n">
+      <c r="E12" s="319" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="317">
+      <c r="F12" s="319">
         <f>1+2+1</f>
         <v/>
       </c>
@@ -3005,7 +3005,7 @@
           <t>16cut/Lt.Sapphire AB/SS16/Non/011+</t>
         </is>
       </c>
-      <c r="I12" s="355" t="inlineStr">
+      <c r="I12" s="348" t="inlineStr">
         <is>
           <t>011+</t>
         </is>
@@ -3024,10 +3024,10 @@
       <c r="D13" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E13" s="301" t="n">
+      <c r="E13" s="311" t="n">
         <v>73</v>
       </c>
-      <c r="F13" s="301">
+      <c r="F13" s="311">
         <f>4+2+1+1</f>
         <v/>
       </c>
@@ -3055,10 +3055,10 @@
       <c r="D14" s="87" t="n">
         <v>1647</v>
       </c>
-      <c r="E14" s="318" t="n">
+      <c r="E14" s="320" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="318" t="n">
+      <c r="F14" s="320" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="247">
@@ -3073,27 +3073,27 @@
       <c r="I14" s="429" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A15" s="303" t="inlineStr">
+      <c r="A15" s="310" t="inlineStr">
         <is>
           <t>SAPPHIRE AB</t>
         </is>
       </c>
-      <c r="B15" s="303" t="inlineStr">
+      <c r="B15" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C15" s="311" t="n">
+      <c r="C15" s="313" t="n">
         <v>1440</v>
       </c>
-      <c r="D15" s="311" t="n">
+      <c r="D15" s="313" t="n">
         <v>1647</v>
       </c>
-      <c r="E15" s="311">
+      <c r="E15" s="313">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F15" s="303" t="n"/>
+      <c r="F15" s="310" t="n"/>
       <c r="G15" s="243">
         <f>E15-F15</f>
         <v/>
@@ -3103,7 +3103,7 @@
           <t>16cut/Sapphire AB/SS16/Non/013+</t>
         </is>
       </c>
-      <c r="I15" s="355" t="inlineStr">
+      <c r="I15" s="348" t="inlineStr">
         <is>
           <t>013+</t>
         </is>
@@ -3111,22 +3111,22 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A16" s="427" t="n"/>
-      <c r="B16" s="301" t="inlineStr">
+      <c r="B16" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C16" s="312" t="n">
+      <c r="C16" s="314" t="n">
         <v>1440</v>
       </c>
-      <c r="D16" s="312" t="n">
+      <c r="D16" s="314" t="n">
         <v>2133</v>
       </c>
-      <c r="E16" s="312">
+      <c r="E16" s="314">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F16" s="301" t="n"/>
+      <c r="F16" s="311" t="n"/>
       <c r="G16" s="245">
         <f>E16-F16</f>
         <v/>
@@ -3140,21 +3140,21 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A17" s="431" t="n"/>
-      <c r="B17" s="302" t="inlineStr">
+      <c r="B17" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C17" s="313" t="n">
+      <c r="C17" s="315" t="n">
         <v>288</v>
       </c>
-      <c r="D17" s="313" t="n">
+      <c r="D17" s="315" t="n">
         <v>1647</v>
       </c>
-      <c r="E17" s="313" t="n">
+      <c r="E17" s="315" t="n">
         <v>46</v>
       </c>
-      <c r="F17" s="302" t="n"/>
+      <c r="F17" s="312" t="n"/>
       <c r="G17" s="246">
         <f>E17-F17</f>
         <v/>
@@ -3183,10 +3183,10 @@
       <c r="D18" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E18" s="317" t="n">
+      <c r="E18" s="319" t="n">
         <v>50</v>
       </c>
-      <c r="F18" s="317" t="n">
+      <c r="F18" s="319" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="244">
@@ -3198,7 +3198,7 @@
           <t>16cut/Capri Blue AB/SS16/Non/017+</t>
         </is>
       </c>
-      <c r="I18" s="355" t="inlineStr">
+      <c r="I18" s="348" t="inlineStr">
         <is>
           <t>017+</t>
         </is>
@@ -3217,10 +3217,10 @@
       <c r="D19" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E19" s="301" t="n">
+      <c r="E19" s="311" t="n">
         <v>76</v>
       </c>
-      <c r="F19" s="301" t="n">
+      <c r="F19" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="245">
@@ -3247,10 +3247,10 @@
       <c r="D20" s="88" t="n">
         <v>1647</v>
       </c>
-      <c r="E20" s="302" t="n">
+      <c r="E20" s="312" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="318" t="n">
+      <c r="F20" s="320" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="246">
@@ -3281,10 +3281,10 @@
       <c r="D21" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E21" s="317" t="n">
+      <c r="E21" s="319" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="303" t="n">
+      <c r="F21" s="310" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="243">
@@ -3296,7 +3296,7 @@
           <t>16cut/Indicolite AB/SS16/Non/014+</t>
         </is>
       </c>
-      <c r="I21" s="355" t="inlineStr">
+      <c r="I21" s="348" t="inlineStr">
         <is>
           <t>014+</t>
         </is>
@@ -3315,10 +3315,10 @@
       <c r="D22" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E22" s="301" t="n">
+      <c r="E22" s="311" t="n">
         <v>78</v>
       </c>
-      <c r="F22" s="301" t="n">
+      <c r="F22" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="245">
@@ -3345,10 +3345,10 @@
       <c r="D23" s="87" t="n">
         <v>1647</v>
       </c>
-      <c r="E23" s="318" t="n">
+      <c r="E23" s="320" t="n">
         <v>50</v>
       </c>
-      <c r="F23" s="318" t="n">
+      <c r="F23" s="320" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="247">
@@ -3363,26 +3363,26 @@
       <c r="I23" s="429" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A24" s="303" t="inlineStr">
+      <c r="A24" s="310" t="inlineStr">
         <is>
           <t>BLUE ZIRCON AB</t>
         </is>
       </c>
-      <c r="B24" s="303" t="inlineStr">
+      <c r="B24" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C24" s="303" t="n">
+      <c r="C24" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D24" s="85" t="n">
         <v>1647</v>
       </c>
-      <c r="E24" s="303" t="n">
+      <c r="E24" s="310" t="n">
         <v>50</v>
       </c>
-      <c r="F24" s="303" t="n"/>
+      <c r="F24" s="310" t="n"/>
       <c r="G24" s="243">
         <f>E24-F24</f>
         <v/>
@@ -3392,7 +3392,7 @@
           <t>16cut/Blue Zircon/SS16/Non/015+</t>
         </is>
       </c>
-      <c r="I24" s="355" t="inlineStr">
+      <c r="I24" s="348" t="inlineStr">
         <is>
           <t>015+</t>
         </is>
@@ -3400,21 +3400,21 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A25" s="427" t="n"/>
-      <c r="B25" s="301" t="inlineStr">
+      <c r="B25" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C25" s="301" t="n">
+      <c r="C25" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D25" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E25" s="301" t="n">
+      <c r="E25" s="311" t="n">
         <v>76</v>
       </c>
-      <c r="F25" s="301">
+      <c r="F25" s="311">
         <f>2+4</f>
         <v/>
       </c>
@@ -3431,21 +3431,21 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A26" s="431" t="n"/>
-      <c r="B26" s="302" t="inlineStr">
+      <c r="B26" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C26" s="302" t="n">
+      <c r="C26" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D26" s="88" t="n">
         <v>1647</v>
       </c>
-      <c r="E26" s="302" t="n">
+      <c r="E26" s="312" t="n">
         <v>50</v>
       </c>
-      <c r="F26" s="302" t="n"/>
+      <c r="F26" s="312" t="n"/>
       <c r="G26" s="246">
         <f>E26-F26</f>
         <v/>
@@ -3474,10 +3474,10 @@
       <c r="D27" s="85" t="n">
         <v>1252</v>
       </c>
-      <c r="E27" s="303" t="n">
+      <c r="E27" s="310" t="n">
         <v>49</v>
       </c>
-      <c r="F27" s="303">
+      <c r="F27" s="310">
         <f>1+1+3+1</f>
         <v/>
       </c>
@@ -3490,7 +3490,7 @@
           <t>16cut/Aquamarine AB/SS16/Non/016+</t>
         </is>
       </c>
-      <c r="I27" s="355" t="inlineStr">
+      <c r="I27" s="348" t="inlineStr">
         <is>
           <t>016+</t>
         </is>
@@ -3509,10 +3509,10 @@
       <c r="D28" s="86" t="n">
         <v>1858</v>
       </c>
-      <c r="E28" s="301" t="n">
+      <c r="E28" s="311" t="n">
         <v>77</v>
       </c>
-      <c r="F28" s="301">
+      <c r="F28" s="311">
         <f>8+2+5</f>
         <v/>
       </c>
@@ -3540,10 +3540,10 @@
       <c r="D29" s="88" t="n">
         <v>1252</v>
       </c>
-      <c r="E29" s="302" t="n">
+      <c r="E29" s="312" t="n">
         <v>50</v>
       </c>
-      <c r="F29" s="302" t="n">
+      <c r="F29" s="312" t="n">
         <v>3</v>
       </c>
       <c r="G29" s="246">
@@ -3574,10 +3574,10 @@
       <c r="D30" s="85" t="n">
         <v>1647</v>
       </c>
-      <c r="E30" s="303" t="n">
+      <c r="E30" s="310" t="n">
         <v>49</v>
       </c>
-      <c r="F30" s="303" t="n"/>
+      <c r="F30" s="310" t="n"/>
       <c r="G30" s="243">
         <f>E30-F30</f>
         <v/>
@@ -3587,7 +3587,7 @@
           <t>16cut/Lt. Peridot AB/SS16/Non/024+</t>
         </is>
       </c>
-      <c r="I30" s="355" t="inlineStr">
+      <c r="I30" s="348" t="inlineStr">
         <is>
           <t>024+</t>
         </is>
@@ -3606,10 +3606,10 @@
       <c r="D31" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E31" s="301" t="n">
+      <c r="E31" s="311" t="n">
         <v>79</v>
       </c>
-      <c r="F31" s="301">
+      <c r="F31" s="311">
         <f>2+1</f>
         <v/>
       </c>
@@ -3637,10 +3637,10 @@
       <c r="D32" s="88" t="n">
         <v>1647</v>
       </c>
-      <c r="E32" s="302" t="n">
+      <c r="E32" s="312" t="n">
         <v>50</v>
       </c>
-      <c r="F32" s="302" t="n">
+      <c r="F32" s="312" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="246">
@@ -3655,27 +3655,27 @@
       <c r="I32" s="429" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A33" s="311" t="inlineStr">
+      <c r="A33" s="313" t="inlineStr">
         <is>
           <t>EMERALD AB</t>
         </is>
       </c>
-      <c r="B33" s="303" t="inlineStr">
+      <c r="B33" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C33" s="311" t="n">
+      <c r="C33" s="313" t="n">
         <v>1440</v>
       </c>
-      <c r="D33" s="311" t="n">
+      <c r="D33" s="313" t="n">
         <v>1647</v>
       </c>
-      <c r="E33" s="311">
+      <c r="E33" s="313">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F33" s="303" t="n"/>
+      <c r="F33" s="310" t="n"/>
       <c r="G33" s="243">
         <f>E33-F33</f>
         <v/>
@@ -3685,7 +3685,7 @@
           <t>16cut/Emerald AB/SS16/Non/026+</t>
         </is>
       </c>
-      <c r="I33" s="355" t="inlineStr">
+      <c r="I33" s="348" t="inlineStr">
         <is>
           <t>026+</t>
         </is>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A34" s="427" t="n"/>
-      <c r="B34" s="301" t="inlineStr">
+      <c r="B34" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C34" s="312" t="n">
+      <c r="C34" s="314" t="n">
         <v>1440</v>
       </c>
-      <c r="D34" s="312" t="n">
+      <c r="D34" s="314" t="n">
         <v>2133</v>
       </c>
-      <c r="E34" s="312">
+      <c r="E34" s="314">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F34" s="301" t="n">
+      <c r="F34" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="245">
@@ -3724,22 +3724,22 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A35" s="431" t="n"/>
-      <c r="B35" s="302" t="inlineStr">
+      <c r="B35" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C35" s="313" t="n">
+      <c r="C35" s="315" t="n">
         <v>288</v>
       </c>
-      <c r="D35" s="313" t="n">
+      <c r="D35" s="315" t="n">
         <v>1647</v>
       </c>
-      <c r="E35" s="313">
+      <c r="E35" s="315">
         <f>25+25</f>
         <v/>
       </c>
-      <c r="F35" s="302" t="n"/>
+      <c r="F35" s="312" t="n"/>
       <c r="G35" s="246">
         <f>E35-F35</f>
         <v/>
@@ -3752,7 +3752,7 @@
       <c r="I35" s="429" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A36" s="354" t="inlineStr">
+      <c r="A36" s="352" t="inlineStr">
         <is>
           <t>OLIVINE AB</t>
         </is>
@@ -3768,10 +3768,10 @@
       <c r="D36" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E36" s="317" t="n">
+      <c r="E36" s="319" t="n">
         <v>49</v>
       </c>
-      <c r="F36" s="317" t="n"/>
+      <c r="F36" s="319" t="n"/>
       <c r="G36" s="244">
         <f>E36-F36</f>
         <v/>
@@ -3781,7 +3781,7 @@
           <t>16cut/Olivine AB/SS16/Non/027+</t>
         </is>
       </c>
-      <c r="I36" s="355" t="inlineStr">
+      <c r="I36" s="348" t="inlineStr">
         <is>
           <t>027+</t>
         </is>
@@ -3828,10 +3828,10 @@
       <c r="D38" s="87" t="n">
         <v>1647</v>
       </c>
-      <c r="E38" s="318" t="n">
+      <c r="E38" s="320" t="n">
         <v>50</v>
       </c>
-      <c r="F38" s="318" t="n"/>
+      <c r="F38" s="320" t="n"/>
       <c r="G38" s="242">
         <f>E38-F38</f>
         <v/>
@@ -3844,27 +3844,27 @@
       <c r="I38" s="429" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A39" s="311" t="inlineStr">
+      <c r="A39" s="313" t="inlineStr">
         <is>
           <t>SIAM AB</t>
         </is>
       </c>
-      <c r="B39" s="303" t="inlineStr">
+      <c r="B39" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C39" s="311" t="n">
+      <c r="C39" s="313" t="n">
         <v>1440</v>
       </c>
-      <c r="D39" s="311" t="n">
+      <c r="D39" s="313" t="n">
         <v>1679</v>
       </c>
-      <c r="E39" s="311">
+      <c r="E39" s="313">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F39" s="303" t="n"/>
+      <c r="F39" s="310" t="n"/>
       <c r="G39" s="243">
         <f>E39-F39</f>
         <v/>
@@ -3874,7 +3874,7 @@
           <t>16cut/Siam AB/SS16/Non/032+</t>
         </is>
       </c>
-      <c r="I39" s="355" t="inlineStr">
+      <c r="I39" s="348" t="inlineStr">
         <is>
           <t>032+</t>
         </is>
@@ -3882,22 +3882,22 @@
     </row>
     <row r="40" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A40" s="427" t="n"/>
-      <c r="B40" s="301" t="inlineStr">
+      <c r="B40" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C40" s="312" t="n">
+      <c r="C40" s="314" t="n">
         <v>1440</v>
       </c>
-      <c r="D40" s="312" t="n">
+      <c r="D40" s="314" t="n">
         <v>2166</v>
       </c>
-      <c r="E40" s="312">
+      <c r="E40" s="314">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F40" s="301" t="n"/>
+      <c r="F40" s="311" t="n"/>
       <c r="G40" s="245">
         <f>E40-F40</f>
         <v/>
@@ -3911,22 +3911,22 @@
     </row>
     <row r="41" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A41" s="431" t="n"/>
-      <c r="B41" s="302" t="inlineStr">
+      <c r="B41" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C41" s="313" t="n">
+      <c r="C41" s="315" t="n">
         <v>288</v>
       </c>
-      <c r="D41" s="313" t="n">
+      <c r="D41" s="315" t="n">
         <v>1679</v>
       </c>
-      <c r="E41" s="313">
+      <c r="E41" s="315">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F41" s="302" t="n"/>
+      <c r="F41" s="312" t="n"/>
       <c r="G41" s="246">
         <f>E41-F41</f>
         <v/>
@@ -3939,27 +3939,27 @@
       <c r="I41" s="429" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A42" s="303" t="inlineStr">
+      <c r="A42" s="310" t="inlineStr">
         <is>
           <t>GARNET AB</t>
         </is>
       </c>
-      <c r="B42" s="303" t="inlineStr">
+      <c r="B42" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C42" s="303" t="n">
+      <c r="C42" s="310" t="n">
         <v>1440</v>
       </c>
-      <c r="D42" s="303" t="n">
+      <c r="D42" s="310" t="n">
         <v>1679</v>
       </c>
-      <c r="E42" s="303">
+      <c r="E42" s="310">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F42" s="303" t="n"/>
+      <c r="F42" s="310" t="n"/>
       <c r="G42" s="243">
         <f>E42-F42</f>
         <v/>
@@ -3969,7 +3969,7 @@
           <t>16cut/Garnet AB/SS16/Non/034+</t>
         </is>
       </c>
-      <c r="I42" s="355" t="inlineStr">
+      <c r="I42" s="348" t="inlineStr">
         <is>
           <t>034+</t>
         </is>
@@ -3977,22 +3977,22 @@
     </row>
     <row r="43" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A43" s="427" t="n"/>
-      <c r="B43" s="301" t="inlineStr">
+      <c r="B43" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C43" s="301" t="n">
+      <c r="C43" s="311" t="n">
         <v>1440</v>
       </c>
-      <c r="D43" s="301" t="n">
+      <c r="D43" s="311" t="n">
         <v>2166</v>
       </c>
-      <c r="E43" s="301">
+      <c r="E43" s="311">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F43" s="301" t="n"/>
+      <c r="F43" s="311" t="n"/>
       <c r="G43" s="245">
         <f>E43-F43</f>
         <v/>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="44" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A44" s="431" t="n"/>
-      <c r="B44" s="302" t="inlineStr">
+      <c r="B44" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C44" s="302" t="n">
+      <c r="C44" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D44" s="302" t="n">
+      <c r="D44" s="312" t="n">
         <v>1679</v>
       </c>
-      <c r="E44" s="302">
+      <c r="E44" s="312">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F44" s="302" t="n"/>
+      <c r="F44" s="312" t="n"/>
       <c r="G44" s="246">
         <f>E44-F44</f>
         <v/>
@@ -4050,10 +4050,10 @@
       <c r="D45" s="140" t="n">
         <v>1679</v>
       </c>
-      <c r="E45" s="317" t="n">
+      <c r="E45" s="319" t="n">
         <v>49</v>
       </c>
-      <c r="F45" s="317">
+      <c r="F45" s="319">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -4066,7 +4066,7 @@
           <t>16cut/Hyacinth AB/SS16/Non/031+</t>
         </is>
       </c>
-      <c r="I45" s="355" t="inlineStr">
+      <c r="I45" s="348" t="inlineStr">
         <is>
           <t>031+</t>
         </is>
@@ -4085,10 +4085,10 @@
       <c r="D46" s="86" t="n">
         <v>2166</v>
       </c>
-      <c r="E46" s="301" t="n">
+      <c r="E46" s="311" t="n">
         <v>78</v>
       </c>
-      <c r="F46" s="301">
+      <c r="F46" s="311">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -4116,10 +4116,10 @@
       <c r="D47" s="88" t="n">
         <v>1679</v>
       </c>
-      <c r="E47" s="302" t="n">
+      <c r="E47" s="312" t="n">
         <v>90</v>
       </c>
-      <c r="F47" s="302">
+      <c r="F47" s="312">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -4135,26 +4135,26 @@
       <c r="I47" s="429" t="n"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A48" s="303" t="inlineStr">
+      <c r="A48" s="310" t="inlineStr">
         <is>
           <t>CITRINE AB</t>
         </is>
       </c>
-      <c r="B48" s="303" t="inlineStr">
+      <c r="B48" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C48" s="303" t="n">
+      <c r="C48" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D48" s="85" t="n">
         <v>1809</v>
       </c>
-      <c r="E48" s="303" t="n">
+      <c r="E48" s="310" t="n">
         <v>40</v>
       </c>
-      <c r="F48" s="303" t="n">
+      <c r="F48" s="310" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="243">
@@ -4166,7 +4166,7 @@
           <t>16cut/Citrine AB/SS16/Non/035+</t>
         </is>
       </c>
-      <c r="I48" s="355" t="inlineStr">
+      <c r="I48" s="348" t="inlineStr">
         <is>
           <t>035+</t>
         </is>
@@ -4174,21 +4174,21 @@
     </row>
     <row r="49" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A49" s="427" t="n"/>
-      <c r="B49" s="301" t="inlineStr">
+      <c r="B49" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C49" s="301" t="n">
+      <c r="C49" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D49" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E49" s="301" t="n">
+      <c r="E49" s="311" t="n">
         <v>50</v>
       </c>
-      <c r="F49" s="301" t="n">
+      <c r="F49" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="245">
@@ -4204,21 +4204,21 @@
     </row>
     <row r="50" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A50" s="431" t="n"/>
-      <c r="B50" s="302" t="inlineStr">
+      <c r="B50" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C50" s="302" t="n">
+      <c r="C50" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D50" s="88" t="n">
         <v>1809</v>
       </c>
-      <c r="E50" s="302" t="n">
+      <c r="E50" s="312" t="n">
         <v>40</v>
       </c>
-      <c r="F50" s="302" t="n">
+      <c r="F50" s="312" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="246">
@@ -4238,21 +4238,21 @@
           <t xml:space="preserve">Lt. Rose AB </t>
         </is>
       </c>
-      <c r="B51" s="303" t="inlineStr">
+      <c r="B51" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C51" s="303" t="n">
+      <c r="C51" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D51" s="85" t="n">
         <v>2000</v>
       </c>
-      <c r="E51" s="303" t="n">
+      <c r="E51" s="310" t="n">
         <v>3</v>
       </c>
-      <c r="F51" s="303">
+      <c r="F51" s="310">
         <f>1+2</f>
         <v/>
       </c>
@@ -4265,7 +4265,7 @@
           <t>16cut/Lt.Rose AB/SS16/Non/038+</t>
         </is>
       </c>
-      <c r="I51" s="355" t="inlineStr">
+      <c r="I51" s="348" t="inlineStr">
         <is>
           <t>038+</t>
         </is>
@@ -4273,21 +4273,21 @@
     </row>
     <row r="52" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A52" s="430" t="n"/>
-      <c r="B52" s="302" t="inlineStr">
+      <c r="B52" s="312" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C52" s="302" t="n">
+      <c r="C52" s="312" t="n">
         <v>1440</v>
       </c>
       <c r="D52" s="88" t="n">
         <v>2500</v>
       </c>
-      <c r="E52" s="302" t="n">
+      <c r="E52" s="312" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="302">
+      <c r="F52" s="312">
         <f>1+2</f>
         <v/>
       </c>
@@ -4303,23 +4303,23 @@
       <c r="I52" s="429" t="n"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A53" s="351" t="inlineStr">
+      <c r="A53" s="349" t="inlineStr">
         <is>
           <t>AQUA SILVER</t>
         </is>
       </c>
-      <c r="B53" s="303" t="inlineStr">
+      <c r="B53" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C53" s="311" t="n">
+      <c r="C53" s="313" t="n">
         <v>1440</v>
       </c>
-      <c r="D53" s="311" t="n">
+      <c r="D53" s="313" t="n">
         <v>968</v>
       </c>
-      <c r="E53" s="311">
+      <c r="E53" s="313">
         <f>10+10</f>
         <v/>
       </c>
@@ -4335,7 +4335,7 @@
           <t>16cut/Aqua Silver/SS16/Non/201+</t>
         </is>
       </c>
-      <c r="I53" s="355" t="inlineStr">
+      <c r="I53" s="348" t="inlineStr">
         <is>
           <t>201+</t>
         </is>
@@ -4343,18 +4343,18 @@
     </row>
     <row r="54" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A54" s="427" t="n"/>
-      <c r="B54" s="301" t="inlineStr">
+      <c r="B54" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C54" s="312" t="n">
+      <c r="C54" s="314" t="n">
         <v>1440</v>
       </c>
-      <c r="D54" s="312" t="n">
+      <c r="D54" s="314" t="n">
         <v>1540</v>
       </c>
-      <c r="E54" s="312">
+      <c r="E54" s="314">
         <f>10+10</f>
         <v/>
       </c>
@@ -4375,18 +4375,18 @@
     </row>
     <row r="55" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A55" s="431" t="n"/>
-      <c r="B55" s="302" t="inlineStr">
+      <c r="B55" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C55" s="313" t="n">
+      <c r="C55" s="315" t="n">
         <v>288</v>
       </c>
-      <c r="D55" s="313" t="n">
+      <c r="D55" s="315" t="n">
         <v>968</v>
       </c>
-      <c r="E55" s="313">
+      <c r="E55" s="315">
         <f>10+9</f>
         <v/>
       </c>
@@ -4416,8 +4416,8 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A21:A23"/>
     <mergeCell ref="I18:I20"/>
-    <mergeCell ref="A21:A23"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="I48:I50"/>
     <mergeCell ref="I39:I41"/>
@@ -4425,32 +4425,32 @@
     <mergeCell ref="A33:A35"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="A53:A55"/>
-    <mergeCell ref="I33:I35"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="I15:I17"/>
-    <mergeCell ref="A24:A26"/>
     <mergeCell ref="I9:I11"/>
+    <mergeCell ref="A42:A44"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="I27:I29"/>
     <mergeCell ref="A36:A38"/>
-    <mergeCell ref="I27:I29"/>
     <mergeCell ref="A30:A32"/>
-    <mergeCell ref="I36:I38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A45:A47"/>
+    <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>
+    <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
-    <mergeCell ref="A48:A50"/>
     <mergeCell ref="I51:I52"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="I53:I55"/>
+    <mergeCell ref="A3:A5"/>
     <mergeCell ref="I12:I14"/>
-    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A27:A29"/>
     <mergeCell ref="I21:I23"/>
-    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="I33:I35"/>
     <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I42:I44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
